--- a/patch_bin/aic8820H/AIC8820H_APC_5G_MCS11_20240708_V2.xlsx
+++ b/patch_bin/aic8820H/AIC8820H_APC_5G_MCS11_20240708_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540" activeTab="5"/>
+    <workbookView windowWidth="14835" windowHeight="13620"/>
   </bookViews>
   <sheets>
     <sheet name="CH42" sheetId="1" r:id="rId1"/>
